--- a/examples/extensions/thai_bim/examples/stair-Straight-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stair-Straight-BBS.xlsx
@@ -228,7 +228,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -904,12 +904,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed310d65f63a4026</t>
+          <t xml:space="preserve">f12ce819f9d94c67</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -977,12 +977,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1fb744779b9c4142</t>
+          <t xml:space="preserve">8b2df0acfea0419b</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1050,12 +1050,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">43d48a92beaa448e</t>
+          <t xml:space="preserve">3e5b6fb7dd5c4194</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ece79bc2a7494a3d</t>
+          <t xml:space="preserve">715d70d45f5f4f77</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1196,12 +1196,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e726dcf2fdb34d29</t>
+          <t xml:space="preserve">469d5a380d9b4cad</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a48bf46170f34b65</t>
+          <t xml:space="preserve">9a440be4c4f9406b</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d1a0ebee02124971</t>
+          <t xml:space="preserve">63cc20df111f4519</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3eef450105b24509</t>
+          <t xml:space="preserve">8b50769976a04f9a</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -1488,12 +1488,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e51d220448c647ec</t>
+          <t xml:space="preserve">2e0b9a1d9a794db0</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c8b2228ec4704bab</t>
+          <t xml:space="preserve">a1613cf7a9f64e9c</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -1634,12 +1634,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e77b49386cf74ffc</t>
+          <t xml:space="preserve">1902c794c9b149b9</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8f488c5ce6834e8f</t>
+          <t xml:space="preserve">3a38920acd5f445a</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2c74c633ec0841f6</t>
+          <t xml:space="preserve">34e89a01ebd344cf</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">04af1ccce8974eb6</t>
+          <t xml:space="preserve">41eec70a5edb48e3</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d665e4ce34b541a3</t>
+          <t xml:space="preserve">ba9dba2e09df4bdf</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800df33b3da4aa2</t>
+          <t xml:space="preserve">c700794a5fd540d8</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2072,12 +2072,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b12382c91f848c2</t>
+          <t xml:space="preserve">6fae42c7f55741aa</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7ee15d7ccebf4930</t>
+          <t xml:space="preserve">66740560bc944e63</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2218,12 +2218,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d2560968cd824fcf</t>
+          <t xml:space="preserve">758a8cae97434be8</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d3bbc8a149144275</t>
+          <t xml:space="preserve">544a70be49b14c0e</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -2364,12 +2364,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214b67ad53b48ad</t>
+          <t xml:space="preserve">c78173fc28a9474a</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2437,12 +2437,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9af650fd6fe14be2</t>
+          <t xml:space="preserve">eac5041906194cf9</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">61c74cf449b844f3</t>
+          <t xml:space="preserve">a90c5305fc2c4c55</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e50583135f7d4ea2</t>
+          <t xml:space="preserve">c92e690a62314297</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6899ca90ca374152</t>
+          <t xml:space="preserve">d8443157b8b84bc2</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -2729,12 +2729,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8522e10fe4394cf8</t>
+          <t xml:space="preserve">9d11309fb8074bfc</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c7f67f4ab5e04dab</t>
+          <t xml:space="preserve">89affa27b6d8428b</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -2875,12 +2875,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bcd5dc4444ac4755</t>
+          <t xml:space="preserve">f3e15f988a2f444a</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -2948,12 +2948,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eaeb1d7d1866435d</t>
+          <t xml:space="preserve">3c95635502a24ab1</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3021,12 +3021,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">07a6aa268e7b4ff1</t>
+          <t xml:space="preserve">3821dd7d44334860</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3094,12 +3094,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">89ecd9e7033e48ed</t>
+          <t xml:space="preserve">2bbf64ecfea64e23</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8087d2cb08654135</t>
+          <t xml:space="preserve">b20dd1881eb649f4</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3240,12 +3240,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">37ec1c80c4864eb9</t>
+          <t xml:space="preserve">bbd06d4a262d4a1e</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3313,12 +3313,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3f565983d6824812</t>
+          <t xml:space="preserve">5d0718a61f764aeb</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3386,12 +3386,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0f173520e35a48ae</t>
+          <t xml:space="preserve">5938867fe09644a6</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f755f6c124f447fd</t>
+          <t xml:space="preserve">af49f69e53fd436c</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3532,12 +3532,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">856443b81c7a4b8e</t>
+          <t xml:space="preserve">71344e3888494611</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -3605,12 +3605,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4fc2005484884daf</t>
+          <t xml:space="preserve">3b523883363842db</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -3678,12 +3678,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c186d5e17a9349f8</t>
+          <t xml:space="preserve">54aa8a8d1bee407b</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -3751,12 +3751,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e0dcdcac2e674871</t>
+          <t xml:space="preserve">ee88418ee0fc4d2f</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -3824,12 +3824,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e2e378f440824d8a</t>
+          <t xml:space="preserve">1aa3e6af1dec4906</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -3897,12 +3897,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">531c90d1b0354568</t>
+          <t xml:space="preserve">d2f5ab01d77642be</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -3970,12 +3970,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2794947bda634840</t>
+          <t xml:space="preserve">6aa86d09db244a75</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4043,12 +4043,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4f28d0c821444112</t>
+          <t xml:space="preserve">b49a3ff858d742eb</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4116,12 +4116,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d0e32e68088a4e10</t>
+          <t xml:space="preserve">be273d63c6bb41ed</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4189,12 +4189,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6270f6fc46e443df</t>
+          <t xml:space="preserve">03076b4850764c4d</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -4262,12 +4262,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e5d6ba01de9f4910</t>
+          <t xml:space="preserve">cc97851c0d074698</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -4335,12 +4335,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2cbb6c17ff154dbf</t>
+          <t xml:space="preserve">48c2fd9551f54f35</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -4408,12 +4408,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ee5e54b073b348d6</t>
+          <t xml:space="preserve">8c06ef478e8643c9</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -4481,12 +4481,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed6ce63f0e2b4938</t>
+          <t xml:space="preserve">fe77aa7945534001</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -4554,12 +4554,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d42a7c91a5884d49</t>
+          <t xml:space="preserve">081b9e2d0d8b48cb</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -4627,12 +4627,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cb87c896cd19405f</t>
+          <t xml:space="preserve">adb23a28436f4f04</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -4700,12 +4700,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9ac972b9968b4142</t>
+          <t xml:space="preserve">102e1cf25dcf4449</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fa6c914c675e4d4b</t>
+          <t xml:space="preserve">40739abe650749ac</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -4846,12 +4846,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3b4502830de042ed</t>
+          <t xml:space="preserve">0e6306a2a08d4cf7</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -4919,12 +4919,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">94ee1a5c91fe469a</t>
+          <t xml:space="preserve">0509a6064c2a4afa</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -4992,12 +4992,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbdebbf1f9b741ce</t>
+          <t xml:space="preserve">e158a92dd8f44280</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5065,12 +5065,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">52361b5d5ec34df6</t>
+          <t xml:space="preserve">a1d742e546864822</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5138,12 +5138,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">29441875dacc42f2</t>
+          <t xml:space="preserve">a63c24cbc31145bc</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5211,12 +5211,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a5d8c416889d4470</t>
+          <t xml:space="preserve">37d941b398064db0</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -5284,12 +5284,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">57f5619a40284e2b</t>
+          <t xml:space="preserve">60b90efff0064241</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -5357,12 +5357,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fb51d19b23e24ecf</t>
+          <t xml:space="preserve">01af38b6080145b4</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -5430,12 +5430,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">725e7f0eb3b944da</t>
+          <t xml:space="preserve">ba77e60701894dbd</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -5503,12 +5503,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eca12cd603b44e66</t>
+          <t xml:space="preserve">1ce3b2c128264a37</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1d3344353e874b36</t>
+          <t xml:space="preserve">e0fe8abb95044a4c</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
